--- a/data/sample/mineria_hidrocarburos_202603.xlsx
+++ b/data/sample/mineria_hidrocarburos_202603.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\JC2026\AGENTE_REPORTES\data\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03 PROYECTOS\agente-reportes-economicos\data\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C77A765-7459-430A-ADE2-9F91FD4E1BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880F7C72-3891-4307-B0C0-43F1CEFCC7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="14100" windowHeight="11295" xr2:uid="{8EFFB3D2-6B7E-4748-B1C0-079B24D71080}"/>
+    <workbookView xWindow="6405" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{8EFFB3D2-6B7E-4748-B1C0-079B24D71080}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -179,9 +182,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -219,7 +222,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -325,7 +328,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -467,7 +470,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -512,7 +515,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -521,21 +524,21 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>-5.0006120958525884</v>
+        <v>-4.5593644906430626</v>
       </c>
       <c r="E2">
-        <v>-5.0006120958525839</v>
+        <v>-4.5593644906430653</v>
       </c>
       <c r="F2">
-        <v>-1.0784353960532513</v>
+        <v>-0.89197520538137098</v>
       </c>
       <c r="G2">
-        <v>-1.078435396053256</v>
+        <v>-0.89197520538136488</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -544,205 +547,205 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>-0.39376504299177384</v>
+        <v>0.11488837713156386</v>
       </c>
       <c r="E3">
-        <v>-0.34196453721230907</v>
+        <v>9.9773010868889039E-2</v>
       </c>
       <c r="F3">
-        <v>1.0272590416267064</v>
+        <v>1.2414127830389958</v>
       </c>
       <c r="G3">
-        <v>0.89566478146896122</v>
+        <v>1.0823655942608681</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>-13.076397052855057</v>
+        <v>3.7902517977335179</v>
       </c>
       <c r="E4">
-        <v>-1.2435231345365145</v>
+        <v>1.8133706063591819</v>
       </c>
       <c r="F4">
         <v>3.0568815439100661</v>
       </c>
       <c r="G4">
-        <v>1.4899811890475751</v>
+        <v>1.4901630328186373</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-5.9449075838878684</v>
+        <v>4.5155377338218301</v>
       </c>
       <c r="E5">
-        <v>-0.55175177117796359</v>
+        <v>0.2051691584867773</v>
       </c>
       <c r="F5">
         <v>2.0230919327266719</v>
       </c>
       <c r="G5">
-        <v>0.17726635975226518</v>
+        <v>0.17728799410817297</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>-5.1394679951136624</v>
+        <v>2.9900455399098291</v>
       </c>
       <c r="E6">
-        <v>-0.5192739047312025</v>
+        <v>0.10075251703221581</v>
       </c>
       <c r="F6">
-        <v>2.301280262798528</v>
+        <v>1.2593563074125456</v>
       </c>
       <c r="G6">
-        <v>0.10936881805306746</v>
+        <v>0.13232894350375757</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>-6.7927731483228939</v>
+        <v>-6.1241279246413143</v>
       </c>
       <c r="E7">
-        <v>-0.11939273567179046</v>
+        <v>-2.7095566799056434E-2</v>
       </c>
       <c r="F7">
-        <v>1.9234018709237404</v>
+        <v>2.301280262798528</v>
       </c>
       <c r="G7">
-        <v>6.5292022876446254E-2</v>
+        <v>0.10938216589830037</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>-6.1241279246413143</v>
+        <v>-0.76831412928896725</v>
       </c>
       <c r="E8">
-        <v>-2.7092713294016732E-2</v>
+        <v>-7.7555031981197925E-2</v>
       </c>
       <c r="F8">
-        <v>-0.80555862935523237</v>
+        <v>1.9234018709237404</v>
       </c>
       <c r="G8">
-        <v>-3.4501732259640391E-3</v>
+        <v>6.5299991398295648E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2.9900455399098291</v>
+        <v>-6.7927731483228939</v>
       </c>
       <c r="E9">
-        <v>0.10074190652101128</v>
+        <v>-0.11940531055748929</v>
       </c>
       <c r="F9">
-        <v>-0.51581018446644578</v>
+        <v>-0.80555862935523237</v>
       </c>
       <c r="G9">
-        <v>-5.4255936840882799E-2</v>
+        <v>-3.4505943000788255E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>4.5155377338218301</v>
+        <v>-5.9449075838878684</v>
       </c>
       <c r="E10">
-        <v>0.20514755158583753</v>
+        <v>-0.55180988372072137</v>
       </c>
       <c r="F10">
         <v>-3.9656979296110677</v>
       </c>
       <c r="G10">
-        <v>-6.8359622299751913E-2</v>
+        <v>-6.836796520474879E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>3.7902517977335179</v>
+        <v>-13.076397052855057</v>
       </c>
       <c r="E11">
-        <v>1.813179635555638</v>
+        <v>-1.2436541070047527</v>
       </c>
       <c r="F11">
         <v>-9.2487487419852528</v>
       </c>
       <c r="G11">
-        <v>-0.82017787589379409</v>
+        <v>-0.82027797396146795</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -754,18 +757,18 @@
         <v>-35.413402475403487</v>
       </c>
       <c r="E12">
-        <v>-4.6589432165817053</v>
+        <v>-4.6594339137593535</v>
       </c>
       <c r="F12">
         <v>-15.410564558146646</v>
       </c>
       <c r="G12">
-        <v>-1.9741691542856143</v>
+        <v>-1.9744100904574049</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
@@ -777,18 +780,18 @@
         <v>-44.83406492810326</v>
       </c>
       <c r="E13">
-        <v>-2.4787632528164045</v>
+        <v>-2.4790243253548905</v>
       </c>
       <c r="F13">
         <v>-15.331610633504894</v>
       </c>
       <c r="G13">
-        <v>-0.82081808329132067</v>
+        <v>-0.82091825949268393</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
@@ -800,18 +803,18 @@
         <v>-38.940494907191415</v>
       </c>
       <c r="E14">
-        <v>-1.4771637834389926</v>
+        <v>-1.4773193638068487</v>
       </c>
       <c r="F14">
         <v>-20.220091400069848</v>
       </c>
       <c r="G14">
-        <v>-0.77554390817482299</v>
+        <v>-0.77563855891935807</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
@@ -823,13 +826,13 @@
         <v>-18.337828748379025</v>
       </c>
       <c r="E15">
-        <v>-0.7030161803263083</v>
+        <v>-0.70309022459761428</v>
       </c>
       <c r="F15">
         <v>-10.432240886860185</v>
       </c>
       <c r="G15">
-        <v>-0.37780716281947047</v>
+        <v>-0.3778532720453629</v>
       </c>
     </row>
   </sheetData>
